--- a/Figure_Plot/figure_plot_2_3/settings.xlsx
+++ b/Figure_Plot/figure_plot_2_3/settings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\清华\storage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Research\Release_Open\Figure_Plot\figure_plot_2_3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358C2355-00DF-4A2D-9708-13806395323D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11F7097-3532-4B1B-B651-5D779BD3E94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2723" yWindow="1275" windowWidth="16200" windowHeight="9308" xr2:uid="{5E2A25D4-814D-4CDB-942E-ABE46EAAF569}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5E2A25D4-814D-4CDB-942E-ABE46EAAF569}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -445,10 +434,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A6B644-B456-42DB-8F5D-ECDC91EAFAFF}">
-  <dimension ref="A1:Y18"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:X18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25" ht="16.149999999999999" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:24" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -521,11 +510,8 @@
       <c r="X1" s="1">
         <v>0.6542</v>
       </c>
-      <c r="Y1" s="1">
-        <v>0.6542</v>
-      </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -598,11 +584,8 @@
       <c r="X2">
         <v>78.919976797482178</v>
       </c>
-      <c r="Y2">
-        <v>75.909977682423616</v>
-      </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -675,11 +658,8 @@
       <c r="X3">
         <v>40.918700000000001</v>
       </c>
-      <c r="Y3">
-        <v>40.668399999999998</v>
-      </c>
     </row>
-    <row r="11" spans="1:25" ht="16.149999999999999" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -705,7 +685,7 @@
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1</v>
       </c>
@@ -713,7 +693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>0</v>
       </c>
